--- a/数据表/AbilityConfig.xlsx
+++ b/数据表/AbilityConfig.xlsx
@@ -2,13 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
+    <sheet name="AbilityConfig" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AbilityConfig!$A$1:$K$18</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,11 +30,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>KeyName</t>
+  </si>
+  <si>
     <t>名字</t>
   </si>
   <si>
@@ -44,22 +50,13 @@
     <t>目标阵营 1：敌方，2：己方，3：自身</t>
   </si>
   <si>
-    <t>目标选择方式 1：手动指定，2：碰撞检测</t>
+    <t>目标选择方式 1:无  2：手动指定，3：碰撞检测, 4: 条件指定</t>
   </si>
   <si>
     <t>冷却时间</t>
   </si>
   <si>
-    <t>Buff类型 1：虚弱，2：强化</t>
-  </si>
-  <si>
-    <t>显示在状态栏</t>
-  </si>
-  <si>
-    <t>能否叠加</t>
-  </si>
-  <si>
-    <t>KeyName</t>
+    <t>Buff类型  1：None  2：虚弱，3 ：强化</t>
   </si>
   <si>
     <t>Name</t>
@@ -83,12 +80,6 @@
     <t>BuffType</t>
   </si>
   <si>
-    <t>StatusSlot</t>
-  </si>
-  <si>
-    <t>CanStack</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -104,21 +95,6 @@
     <t>眩晕</t>
   </si>
   <si>
-    <t>Buff</t>
-  </si>
-  <si>
-    <t>敌方</t>
-  </si>
-  <si>
-    <t>Weaken</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
     <t>Mute</t>
   </si>
   <si>
@@ -131,33 +107,18 @@
     <t>黑火球术</t>
   </si>
   <si>
-    <t>Skill</t>
-  </si>
-  <si>
-    <t>手动指定</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>FireExplode</t>
   </si>
   <si>
     <t>炎爆</t>
   </si>
   <si>
-    <t>碰撞检测</t>
-  </si>
-  <si>
     <t>Cure</t>
   </si>
   <si>
     <t>治愈</t>
   </si>
   <si>
-    <t>己方</t>
-  </si>
-  <si>
     <t>血红激光炮</t>
   </si>
   <si>
@@ -170,9 +131,6 @@
     <t>灵魂锁链</t>
   </si>
   <si>
-    <t>条件指定</t>
-  </si>
-  <si>
     <t>火球</t>
   </si>
   <si>
@@ -182,9 +140,6 @@
     <t>光盾</t>
   </si>
   <si>
-    <t>自身</t>
-  </si>
-  <si>
     <t>Weak</t>
   </si>
   <si>
@@ -201,9 +156,6 @@
   </si>
   <si>
     <t>护盾</t>
-  </si>
-  <si>
-    <t>Enhance</t>
   </si>
   <si>
     <t>Shield2</t>
@@ -842,8 +794,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -855,13 +810,31 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1214,521 +1187,525 @@
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="12.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12" style="4" customWidth="1"/>
-    <col min="4" max="4" width="41.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="30.75" style="3" customWidth="1"/>
-    <col min="6" max="6" width="38.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="17.875" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="1" max="2" width="12.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="12" style="5" customWidth="1"/>
+    <col min="4" max="4" width="41.875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="30.75" style="4" customWidth="1"/>
+    <col min="6" max="6" width="38.75" style="4" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="9.625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13" style="4" customWidth="1"/>
+    <col min="10" max="10" width="15.125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="17.875" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.5" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="1" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:11">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>9</v>
       </c>
+      <c r="D2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
-      <c r="A2" s="5" t="s">
+    <row r="3" s="2" customFormat="1" spans="1:11">
+      <c r="A3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" s="3" customFormat="1" spans="1:9">
+      <c r="A4" s="3">
+        <v>101</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="13">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>19</v>
+      <c r="I4" s="3">
+        <v>2</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
-      <c r="A3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="5" s="3" customFormat="1" spans="1:9">
+      <c r="A5" s="3">
+        <v>102</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="C5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>21</v>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="13">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>2</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:11">
-      <c r="A4" s="2">
-        <v>101</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="6" s="3" customFormat="1" spans="1:9">
+      <c r="A6" s="3">
+        <v>1001</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="2" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="12">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="1:9">
+      <c r="A7" s="3">
+        <v>1002</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="C7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="2" t="s">
+      <c r="D7" s="10"/>
+      <c r="E7" s="12">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:9">
+      <c r="A8" s="3">
+        <v>1003</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="C8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="D8" s="10"/>
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:9">
+      <c r="A9" s="3">
+        <v>1004</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10" t="s">
         <v>29</v>
       </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="12">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:11">
-      <c r="A5" s="2">
-        <v>102</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="10" s="2" customFormat="1" spans="1:9">
+      <c r="A10" s="3">
+        <v>1005</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>29</v>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:9">
-      <c r="A6" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="11" s="2" customFormat="1" spans="1:9">
+      <c r="A11" s="3">
+        <v>1006</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D11" s="11"/>
+      <c r="E11" s="12">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3">
+        <v>2</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:9">
+      <c r="A12" s="3">
+        <v>1008</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="D12" s="11"/>
+      <c r="E12" s="12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:9">
+      <c r="A13" s="3">
+        <v>3001</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="D13" s="11"/>
+      <c r="E13" s="12">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3">
+        <v>2</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:9">
+      <c r="A14" s="3">
+        <v>2001</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="2">
+      <c r="D14" s="11"/>
+      <c r="E14" s="12">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:11">
+      <c r="A15" s="3">
+        <v>10011</v>
+      </c>
+      <c r="B15" s="14" t="s">
         <v>36</v>
       </c>
+      <c r="C15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="13">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:9">
-      <c r="A7" s="2">
-        <v>1002</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="2" t="s">
+    <row r="16" s="2" customFormat="1" spans="1:11">
+      <c r="A16" s="3">
+        <v>10041</v>
+      </c>
+      <c r="B16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="C16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="2">
+      <c r="D16" s="11"/>
+      <c r="E16" s="12">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="13">
         <v>0</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="I16" s="3">
+        <v>2</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:9">
-      <c r="A8" s="2">
-        <v>1003</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="17" s="2" customFormat="1" spans="1:11">
+      <c r="A17" s="3">
+        <v>20011</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C17" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="D17" s="11"/>
+      <c r="E17" s="12">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="13">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:11">
+      <c r="A18" s="3">
+        <v>20012</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="2">
+      <c r="C18" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="12">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="13">
         <v>0</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:9">
-      <c r="A9" s="2">
-        <v>1004</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:9">
-      <c r="A10" s="2">
-        <v>1005</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:9">
-      <c r="A11" s="2">
-        <v>1006</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:9">
-      <c r="A12" s="2">
-        <v>1008</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:9">
-      <c r="A13" s="2">
-        <v>3001</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:9">
-      <c r="A14" s="2">
-        <v>2001</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:11">
-      <c r="A15" s="2">
-        <v>10011</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:11">
-      <c r="A16" s="2">
-        <v>10041</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:11">
-      <c r="A17" s="2">
-        <v>20011</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:11">
-      <c r="A18" s="2">
-        <v>20012</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="I18" s="3">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E18">
-      <formula1>"Skill,Buff"</formula1>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E7 E8:E14 E15:E18">
+      <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F18">
-      <formula1>"自身,己方,敌方"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F18 I4:I5 I6:I14 I15:I18">
+      <formula1>"1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:G14">
-      <formula1>"手动指定,碰撞检测,条件指定"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I18">
-      <formula1>"Weaken,Enhance,None"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G18">
+      <formula1>"1,2,3,4"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:K6 J15:K18">
       <formula1>"是,否"</formula1>
